--- a/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-14557_Datatype_Parametrized_Constructor_Vocabulary_Validation.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-14557_Datatype_Parametrized_Constructor_Vocabulary_Validation.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="47">
   <si>
     <t>Datatype Gender &lt;String&gt;</t>
   </si>
@@ -244,6 +244,53 @@
     check10 = new String[] {"NY", "NJ"},
     check11 = new String[][] {{"CA"}, {"NY", "NJ"}},
     check12 = new String[][] {{"US"}, {"AB"}},
+    check13 = "Female",
+    check14 = 200,
+    check15 = 300,
+    check16 = null,
+    check17 = null,
+    check18 = 33,
+    check19 = new Level[] {44}
+);</t>
+  </si>
+  <si>
+    <t>Datatype Country &lt;String&gt;</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>NJ</t>
+  </si>
+  <si>
+    <t>= MyDataType(
+    check1 = "Male",
+    check2 = "FMale",
+    check3 = "F3",
+    check4 = 100,
+    check5 = 999,
+    check6 = "AB",
+    check11 = new String[] {"CA" , "NY", "NJ"},
+    check12 = new String[][] {"NY", "NJ"},
+    check13 = "Female",
+    check14 = 200,
+    check15 = 300,
+    check16 = null,
+    check17 = null,
+    check18 = 33,
+    check19 = new Level[] {44}
+);</t>
+  </si>
+  <si>
+    <t>= MyDataType(
+    check1 = "Male",
+    check2 = "FMale",
+    check3 = "F3",
+    check4 = 100,
+    check5 = 999,
+    check6 = "AB",
+    check11 = new String[] {"CA" , "NY", "NJ"},
+    check12 = new String[] {"NY", "NJ"},
     check13 = "Female",
     check14 = 200,
     check15 = 300,
@@ -557,7 +604,7 @@
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C1000"/>
+  <dimension ref="B1:C1005"/>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="8.71"/>
@@ -601,21 +648,9 @@
         <v>300.0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
     <row r="14">
       <c r="B14" s="1" t="s">
         <v>7</v>
@@ -634,7 +669,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -1627,6 +1662,26 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1002">
+      <c r="B1002" t="s" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="B1003" t="s" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="B1004" t="s" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="B1005" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
